--- a/data/sample/Store_Action.xlsx
+++ b/data/sample/Store_Action.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5588BCE2-36B5-4C37-8C1D-41C6CB30978E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07EC555-0292-4F41-B79B-C5C7470F94CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BB575107-6664-4351-B24A-DC96A3AC4071}"/>
   </bookViews>
@@ -160,10 +160,10 @@
     <t>If S08_Active_Season_Flag = 1 AND If S09_Days_To_Season_End &lt;= S01_Weeks_Cover*7, then check for Peer Shortage Flag, else Check for Network Imbalance</t>
   </si>
   <si>
-    <t>If S22_Shelf_Life_Remaining_Days &lt;= S01_Weeks_Cover*7 for any of the batches of this SKU, then "Store Manager to decide between Markdown/Transfer/Dispose/Donate"</t>
-  </si>
-  <si>
     <t>If S22_Shelf_Life_Remaining_Days &gt; S01_Weeks_Cover*7 for all the batches of this SKU, then check for near-expiry batches</t>
+  </si>
+  <si>
+    <t>If S22_Shelf_Life_Remaining_Days &lt;= S01_Weeks_Cover*7 for any of the batches of this SKU, then "Store Manager to decide between Markdown/Transfer/Dispose/Donate for expiry-risk SKU"</t>
   </si>
 </sst>
 </file>
@@ -732,12 +732,12 @@
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
